--- a/artfynd/A 61724-2022 artfynd.xlsx
+++ b/artfynd/A 61724-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 61724-2022 artfynd.xlsx
+++ b/artfynd/A 61724-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>108481075</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
+        <v>100171</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>691730.00377987</v>
+        <v>691730</v>
       </c>
       <c r="R2" t="n">
-        <v>6603247.214110035</v>
+        <v>6603247</v>
       </c>
       <c r="S2" t="n">
         <v>70</v>
@@ -2982,7 +2982,7 @@
         <v>109088868</v>
       </c>
       <c r="B22" t="n">
-        <v>101680</v>
+        <v>103418</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3020,10 +3020,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>691701.5729203466</v>
+        <v>691702</v>
       </c>
       <c r="R22" t="n">
-        <v>6603345.379658982</v>
+        <v>6603346</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>

--- a/artfynd/A 61724-2022 artfynd.xlsx
+++ b/artfynd/A 61724-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>108481075</v>
       </c>
       <c r="B2" t="n">
-        <v>100171</v>
+        <v>100194</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -2982,7 +2982,7 @@
         <v>109088868</v>
       </c>
       <c r="B22" t="n">
-        <v>103418</v>
+        <v>103441</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
